--- a/sources/kuma_step5b.xlsx
+++ b/sources/kuma_step5b.xlsx
@@ -769,6 +769,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
@@ -816,6 +821,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
@@ -863,6 +873,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
@@ -908,6 +923,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>d84f5821-e8c2-4b13-80d7-7f78bb38c6d1</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">

--- a/sources/kuma_step5b.xlsx
+++ b/sources/kuma_step5b.xlsx
@@ -2588,7 +2588,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3084,7 +3084,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4319,7 +4319,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4696,6 +4696,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>– Sitting Claws</t>
@@ -4793,6 +4798,11 @@
       <c r="A81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
